--- a/Carpeta_N3_Base_de_datos_y_codigo/salidas/tabla2_matriz_correlacion.xlsx
+++ b/Carpeta_N3_Base_de_datos_y_codigo/salidas/tabla2_matriz_correlacion.xlsx
@@ -434,7 +434,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>APR total</t>
+          <t>ln(APR)</t>
         </is>
       </c>
     </row>
@@ -448,13 +448,13 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.019</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.281</v>
+        <v>-0.453</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.125</v>
+        <v>-0.497</v>
       </c>
     </row>
     <row r="3">
@@ -464,16 +464,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.019</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.473</v>
+        <v>-0.467</v>
       </c>
       <c r="E3" t="n">
-        <v>0.161</v>
+        <v>0.454</v>
       </c>
     </row>
     <row r="4">
@@ -483,32 +483,32 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.281</v>
+        <v>-0.453</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.473</v>
+        <v>-0.467</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.007</v>
+        <v>0.094</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>APR total</t>
+          <t>ln(APR)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.125</v>
+        <v>-0.497</v>
       </c>
       <c r="C5" t="n">
-        <v>0.161</v>
+        <v>0.454</v>
       </c>
       <c r="D5" t="n">
-        <v>0.007</v>
+        <v>0.094</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
